--- a/list-detectable-swh.xlsx
+++ b/list-detectable-swh.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raps/Documents/02_Work/anomalous-commits/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raps/Documents/02_Work/anomalous-commits.nosync/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BA26019-DE34-C049-A903-8E386C121885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD18F53-16FD-CF46-B9BD-7C3EB2D15701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33520" yWindow="-6120" windowWidth="28040" windowHeight="17440" xr2:uid="{042DB25C-90C8-2848-8C1B-3E44FB8452BF}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19880" xr2:uid="{042DB25C-90C8-2848-8C1B-3E44FB8452BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$38</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,9 +39,191 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="59">
+  <si>
+    <t>Factors</t>
+  </si>
+  <si>
+    <t>SWH Compatibilty</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Compatible</t>
+  </si>
+  <si>
+    <t>Incompatible</t>
+  </si>
+  <si>
+    <t>LOC added</t>
+  </si>
+  <si>
+    <t>LOC removed</t>
+  </si>
+  <si>
+    <t>#Files added</t>
+  </si>
+  <si>
+    <t>#Files removed</t>
+  </si>
+  <si>
+    <t>#Files modified</t>
+  </si>
+  <si>
+    <t>#Files renamed</t>
+  </si>
+  <si>
+    <t>Sensitive file</t>
+  </si>
+  <si>
+    <t>Proportion of ownership</t>
+  </si>
+  <si>
+    <t>Identifiable username</t>
+  </si>
+  <si>
+    <t>Account age</t>
+  </si>
+  <si>
+    <t>Proportion of PR rejected</t>
+  </si>
+  <si>
+    <t>LOC modified</t>
+  </si>
+  <si>
+    <t>#Hunks added</t>
+  </si>
+  <si>
+    <t>#Hunks modified</t>
+  </si>
+  <si>
+    <t>#Hunks deleted</t>
+  </si>
+  <si>
+    <t>Commit message vs commit size</t>
+  </si>
+  <si>
+    <t>Time between commits</t>
+  </si>
+  <si>
+    <t>Time between commits to a file</t>
+  </si>
+  <si>
+    <t>Change in Complexity</t>
+  </si>
+  <si>
+    <t>#Methods added</t>
+  </si>
+  <si>
+    <t>#Methods modified</t>
+  </si>
+  <si>
+    <t>McCabe complexity of all methods touched in a commit</t>
+  </si>
+  <si>
+    <t>File changed by many dev</t>
+  </si>
+  <si>
+    <t>hash same but message (filename) different &amp; no reference to previous filename ?</t>
+  </si>
+  <si>
+    <t>#Open PR</t>
+  </si>
+  <si>
+    <t>Don't Know</t>
+  </si>
+  <si>
+    <t>Amount of open PR in a project vs median amount</t>
+  </si>
+  <si>
+    <t>#Comments on commits</t>
+  </si>
+  <si>
+    <t>#Project created VS forked</t>
+  </si>
+  <si>
+    <t>Fork with no PR</t>
+  </si>
+  <si>
+    <t>Change in repo ownership</t>
+  </si>
+  <si>
+    <t>Introduction of prebuilt binaries</t>
+  </si>
+  <si>
+    <t>Files of types a developer rarely changes personally</t>
+  </si>
+  <si>
+    <t>Only if diff info available</t>
+  </si>
+  <si>
+    <t>Distance between name and email</t>
+  </si>
+  <si>
+    <t>If we deanonimyze</t>
+  </si>
+  <si>
+    <t>Adaptable</t>
+  </si>
+  <si>
+    <t>CF time since 1st commit</t>
+  </si>
+  <si>
+    <t>Don't know how to track that | maybe possible through branch names</t>
+  </si>
+  <si>
+    <t>Only using archived forge metadata</t>
+  </si>
+  <si>
+    <t>extension based</t>
+  </si>
+  <si>
+    <t>extension list</t>
+  </si>
+  <si>
+    <t>Expensive</t>
+  </si>
+  <si>
+    <t>Number of commits for an author in a repo</t>
+  </si>
+  <si>
+    <t>Need diff</t>
+  </si>
+  <si>
+    <t>Implem</t>
+  </si>
+  <si>
+    <t>Done in all repo</t>
+  </si>
+  <si>
+    <t>#Unique file types modified per repo</t>
+  </si>
+  <si>
+    <t>Type of files changed per dev Xrepo</t>
+  </si>
+  <si>
+    <t>Commit-time distribution per author Xrepo</t>
+  </si>
+  <si>
+    <t>Commit-time distribution per repo</t>
+  </si>
+  <si>
+    <t>Time since 1st commit of an author Xrepo</t>
+  </si>
+  <si>
+    <t>Time since 1st commit of an author in a repo</t>
+  </si>
+  <si>
+    <t>Number of commits for an author Xrepo</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -45,13 +231,50 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -63,16 +286,53 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -402,9 +662,459 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E0898F4-33D2-0444-8019-4CDEB75F6B07}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D38" xr:uid="{0E0898F4-33D2-0444-8019-4CDEB75F6B07}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D38">
+      <sortCondition ref="B1:B38"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="B2:B38 D7:D9 D23:D25">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Incompatible">
+      <formula>NOT(ISERROR(SEARCH("Incompatible",B2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Compatible">
+      <formula>NOT(ISERROR(SEARCH("Compatible",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B38">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Don't Know">
+      <formula>NOT(ISERROR(SEARCH("Don't Know",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{069FC0D8-5ACC-D940-9BC4-36367319884E}">
+          <x14:formula1>
+            <xm:f>Sheet2!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>D23:D25</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B2975DD3-2736-8643-9B84-7EB13056AAFE}">
+          <x14:formula1>
+            <xm:f>Sheet2!$A$1:$A$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B38</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B790884C-4816-084E-9054-025CC34F78B1}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>